--- a/Sensitivity analysis/Sensitivity analysis.xlsx
+++ b/Sensitivity analysis/Sensitivity analysis.xlsx
@@ -385,16 +385,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.077025</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="B2">
-        <v>2.308728324280074E-147</v>
+        <v>7.74111461817066E-95</v>
       </c>
       <c r="C2">
-        <v>0.2675</v>
+        <v>0.3006306689342403</v>
       </c>
       <c r="D2">
-        <v>9.449794499962948E-16</v>
+        <v>1.757118450130801E-09</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -402,16 +402,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.07679999999999999</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="B3">
-        <v>1.43003441619528E-147</v>
+        <v>3.15287278228097E-95</v>
       </c>
       <c r="C3">
-        <v>0.268575</v>
+        <v>0.3013038548752834</v>
       </c>
       <c r="D3">
-        <v>1.386967413516723E-15</v>
+        <v>2.038928083225326E-09</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -419,16 +419,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.07635</v>
+        <v>0.09325396825396826</v>
       </c>
       <c r="B4">
-        <v>3.445256432484319E-150</v>
+        <v>7.832201068330619E-95</v>
       </c>
       <c r="C4">
-        <v>0.269825</v>
+        <v>0.3022250566893424</v>
       </c>
       <c r="D4">
-        <v>2.092891136767983E-15</v>
+        <v>2.465836399110761E-09</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -436,16 +436,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.07552499999999999</v>
+        <v>0.09350198412698413</v>
       </c>
       <c r="B5">
-        <v>1.700258669084898E-154</v>
+        <v>2.165494710383675E-95</v>
       </c>
       <c r="C5">
-        <v>0.27075</v>
+        <v>0.3035359977324263</v>
       </c>
       <c r="D5">
-        <v>2.826932371641787E-15</v>
+        <v>3.266548264181864E-09</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -453,16 +453,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.0743</v>
+        <v>0.09204931972789115</v>
       </c>
       <c r="B6">
-        <v>4.691436570225851E-160</v>
+        <v>2.522895536326446E-98</v>
       </c>
       <c r="C6">
-        <v>0.271875</v>
+        <v>0.3050240929705215</v>
       </c>
       <c r="D6">
-        <v>4.05480084907358E-15</v>
+        <v>4.405425148587582E-09</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -470,16 +470,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.07495</v>
+        <v>0.09346655328798185</v>
       </c>
       <c r="B7">
-        <v>7.825772634641915E-159</v>
+        <v>2.574136387959558E-96</v>
       </c>
       <c r="C7">
-        <v>0.27345</v>
+        <v>0.3062996031746032</v>
       </c>
       <c r="D7">
-        <v>6.716093145618674E-15</v>
+        <v>5.757819387396599E-09</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -487,16 +487,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.075825</v>
+        <v>0.0939625850340136</v>
       </c>
       <c r="B8">
-        <v>5.583767284244946E-157</v>
+        <v>8.58899743995105E-96</v>
       </c>
       <c r="C8">
-        <v>0.274475</v>
+        <v>0.3072562358276644</v>
       </c>
       <c r="D8">
-        <v>9.522611747400902E-15</v>
+        <v>6.961836340262211E-09</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -504,16 +504,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.076975</v>
+        <v>0.09481292517006802</v>
       </c>
       <c r="B9">
-        <v>1.430714086007355E-154</v>
+        <v>2.001113363283056E-95</v>
       </c>
       <c r="C9">
-        <v>0.27535</v>
+        <v>0.308531746031746</v>
       </c>
       <c r="D9">
-        <v>1.248853195388933E-14</v>
+        <v>9.021805036605629E-09</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -521,16 +521,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.0759</v>
+        <v>0.09328939909297052</v>
       </c>
       <c r="B10">
-        <v>2.658722704797106E-159</v>
+        <v>1.303362424043252E-98</v>
       </c>
       <c r="C10">
-        <v>0.2773</v>
+        <v>0.3104804421768708</v>
       </c>
       <c r="D10">
-        <v>2.349484519658665E-14</v>
+        <v>1.358496678438934E-08</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -538,16 +538,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.04915</v>
+        <v>0.0586734693877551</v>
       </c>
       <c r="B11">
-        <v>1.79987573609023E-258</v>
+        <v>1.526515827962213E-171</v>
       </c>
       <c r="C11">
-        <v>0.27995</v>
+        <v>0.3138463718820862</v>
       </c>
       <c r="D11">
-        <v>5.67424216813396E-14</v>
+        <v>2.687549391793392E-08</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -555,16 +555,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.0786</v>
+        <v>0.0954861111111111</v>
       </c>
       <c r="B12">
-        <v>1.119783724380918E-149</v>
+        <v>1.299360424744752E-94</v>
       </c>
       <c r="C12">
-        <v>0.28215</v>
+        <v>0.3160076530612245</v>
       </c>
       <c r="D12">
-        <v>1.158688038363393E-13</v>
+        <v>4.162341216434452E-08</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -609,16 +609,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.077025</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="B2">
-        <v>2.308728324280074E-147</v>
+        <v>7.74111461817066E-95</v>
       </c>
       <c r="C2">
-        <v>0.2675</v>
+        <v>0.3006306689342403</v>
       </c>
       <c r="D2">
-        <v>9.449794499962948E-16</v>
+        <v>1.757118450130801E-09</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -626,16 +626,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.076975</v>
+        <v>0.09275793650793651</v>
       </c>
       <c r="B3">
-        <v>1.456950073811214E-147</v>
+        <v>5.920034566558455E-95</v>
       </c>
       <c r="C3">
-        <v>0.262975</v>
+        <v>0.2952097505668934</v>
       </c>
       <c r="D3">
-        <v>1.584250385966018E-16</v>
+        <v>5.054592269885792E-10</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -643,16 +643,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.07667499999999999</v>
+        <v>0.09250992063492064</v>
       </c>
       <c r="B4">
-        <v>2.092203102962256E-148</v>
+        <v>2.861327928869572E-95</v>
       </c>
       <c r="C4">
-        <v>0.251975</v>
+        <v>0.2848639455782313</v>
       </c>
       <c r="D4">
-        <v>1.469937824319415E-18</v>
+        <v>3.477068775149689E-11</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -660,16 +660,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.07642500000000001</v>
+        <v>0.09222647392290249</v>
       </c>
       <c r="B5">
-        <v>3.021144123815628E-149</v>
+        <v>1.176640673931353E-95</v>
       </c>
       <c r="C5">
-        <v>0.235675</v>
+        <v>0.2689200680272109</v>
       </c>
       <c r="D5">
-        <v>6.122809446273696E-22</v>
+        <v>3.791320989619202E-13</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -677,16 +677,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.0766</v>
+        <v>0.09268707482993198</v>
       </c>
       <c r="B6">
-        <v>1.186526467449125E-148</v>
+        <v>5.628995478153802E-95</v>
       </c>
       <c r="C6">
-        <v>0.2178</v>
+        <v>0.2523030045351474</v>
       </c>
       <c r="D6">
-        <v>2.138246723523443E-26</v>
+        <v>1.490723211478517E-15</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -694,16 +694,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.076725</v>
+        <v>0.09311224489795919</v>
       </c>
       <c r="B7">
-        <v>4.178474797474225E-148</v>
+        <v>2.303549519246324E-94</v>
       </c>
       <c r="C7">
-        <v>0.199675</v>
+        <v>0.2329577664399093</v>
       </c>
       <c r="D7">
-        <v>5.499869700338425E-32</v>
+        <v>4.916943731261179E-19</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -711,16 +711,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.077075</v>
+        <v>0.09367913832199547</v>
       </c>
       <c r="B8">
-        <v>4.30071186267256E-147</v>
+        <v>1.341582019926507E-93</v>
       </c>
       <c r="C8">
-        <v>0.1808</v>
+        <v>0.2120535714285714</v>
       </c>
       <c r="D8">
-        <v>2.389186332877066E-39</v>
+        <v>1.212179892521932E-23</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -728,16 +728,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07729999999999999</v>
+        <v>0.09392715419501134</v>
       </c>
       <c r="B9">
-        <v>1.440132874200981E-146</v>
+        <v>3.035038437020045E-93</v>
       </c>
       <c r="C9">
-        <v>0.1641</v>
+        <v>0.1915745464852608</v>
       </c>
       <c r="D9">
-        <v>2.585597671813865E-47</v>
+        <v>3.120680659305024E-29</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -745,16 +745,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.07745</v>
+        <v>0.0946357709750567</v>
       </c>
       <c r="B10">
-        <v>3.593933098030856E-146</v>
+        <v>4.244920502548199E-92</v>
       </c>
       <c r="C10">
-        <v>0.14775</v>
+        <v>0.1725481859410431</v>
       </c>
       <c r="D10">
-        <v>5.577868153120287E-57</v>
+        <v>7.356423622756562E-36</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -762,16 +762,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.078125</v>
+        <v>0.0954861111111111</v>
       </c>
       <c r="B11">
-        <v>3.063537510289005E-144</v>
+        <v>9.120503902334824E-91</v>
       </c>
       <c r="C11">
-        <v>0.1337</v>
+        <v>0.1564271541950113</v>
       </c>
       <c r="D11">
-        <v>2.763304724232375E-67</v>
+        <v>7.868811920211289E-43</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -779,16 +779,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.078975</v>
+        <v>0.09654903628117914</v>
       </c>
       <c r="B12">
-        <v>7.532408706390409E-142</v>
+        <v>2.880581339521268E-89</v>
       </c>
       <c r="C12">
-        <v>0.1222</v>
+        <v>0.1437074829931973</v>
       </c>
       <c r="D12">
-        <v>1.146267740045915E-77</v>
+        <v>1.544113455304959E-49</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.077025</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="B2">
-        <v>2.308728324280074E-147</v>
+        <v>7.74111461817066E-95</v>
       </c>
       <c r="C2">
-        <v>0.2675</v>
+        <v>0.3006306689342403</v>
       </c>
       <c r="D2">
-        <v>9.449794499962948E-16</v>
+        <v>1.757118450130801E-09</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -850,16 +850,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.07679999999999999</v>
+        <v>0.09282879818594104</v>
       </c>
       <c r="B3">
-        <v>9.156151833686001E-148</v>
+        <v>2.859679080330145E-95</v>
       </c>
       <c r="C3">
-        <v>0.264075</v>
+        <v>0.2963081065759637</v>
       </c>
       <c r="D3">
-        <v>2.390992949721171E-16</v>
+        <v>6.403915084277785E-10</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.07645</v>
+        <v>0.09346655328798185</v>
       </c>
       <c r="B4">
-        <v>2.518739774140739E-150</v>
+        <v>1.307610453736503E-94</v>
       </c>
       <c r="C4">
-        <v>0.2545</v>
+        <v>0.2868835034013605</v>
       </c>
       <c r="D4">
-        <v>4.097971094327076E-18</v>
+        <v>5.806612113161748E-11</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -884,16 +884,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.076</v>
+        <v>0.09431689342403628</v>
       </c>
       <c r="B5">
-        <v>1.905791816372801E-153</v>
+        <v>3.042995298143445E-94</v>
       </c>
       <c r="C5">
-        <v>0.23925</v>
+        <v>0.2726757369614513</v>
       </c>
       <c r="D5">
-        <v>3.297615058889159E-21</v>
+        <v>1.116797240163642E-12</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -901,16 +901,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.07580000000000001</v>
+        <v>0.09406887755102041</v>
       </c>
       <c r="B6">
-        <v>5.680869439876855E-156</v>
+        <v>3.444926960185981E-95</v>
       </c>
       <c r="C6">
-        <v>0.222575</v>
+        <v>0.2577593537414966</v>
       </c>
       <c r="D6">
-        <v>3.317306221142837E-25</v>
+        <v>8.696107123019547E-15</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.07765</v>
+        <v>0.09686791383219955</v>
       </c>
       <c r="B7">
-        <v>1.956310063377217E-151</v>
+        <v>1.614805408803615E-91</v>
       </c>
       <c r="C7">
-        <v>0.205725</v>
+        <v>0.2394770408163265</v>
       </c>
       <c r="D7">
-        <v>3.780789123509426E-30</v>
+        <v>6.818541172887411E-18</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -935,16 +935,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.079625</v>
+        <v>0.0988874716553288</v>
       </c>
       <c r="B8">
-        <v>9.8649705640883E-146</v>
+        <v>9.000903954369589E-89</v>
       </c>
       <c r="C8">
-        <v>0.1883</v>
+        <v>0.2197066326530612</v>
       </c>
       <c r="D8">
-        <v>1.965670161880384E-36</v>
+        <v>5.834222691731474E-22</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -952,16 +952,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.082</v>
+        <v>0.101296768707483</v>
       </c>
       <c r="B9">
-        <v>1.519981408619409E-140</v>
+        <v>3.204234580977685E-86</v>
       </c>
       <c r="C9">
-        <v>0.1721</v>
+        <v>0.1997945011337869</v>
       </c>
       <c r="D9">
-        <v>2.179095641321725E-43</v>
+        <v>6.905586549531416E-27</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.0818</v>
+        <v>0.1014384920634921</v>
       </c>
       <c r="B10">
-        <v>9.118031767158835E-142</v>
+        <v>1.770363872676962E-86</v>
       </c>
       <c r="C10">
-        <v>0.156775</v>
+        <v>0.1820082199546485</v>
       </c>
       <c r="D10">
-        <v>2.033874542344825E-51</v>
+        <v>2.0753453151163E-32</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -986,16 +986,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.05215</v>
+        <v>0.06242913832199547</v>
       </c>
       <c r="B11">
-        <v>4.60913016909277E-237</v>
+        <v>2.890593069086034E-157</v>
       </c>
       <c r="C11">
-        <v>0.144325</v>
+        <v>0.1674815759637188</v>
       </c>
       <c r="D11">
-        <v>4.37426255931344E-59</v>
+        <v>8.637967337059903E-38</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.08525000000000001</v>
+        <v>0.1047689909297052</v>
       </c>
       <c r="B12">
-        <v>1.908507540945365E-132</v>
+        <v>4.629385688184152E-82</v>
       </c>
       <c r="C12">
-        <v>0.1345</v>
+        <v>0.1569940476190476</v>
       </c>
       <c r="D12">
-        <v>2.688686188329272E-66</v>
+        <v>2.045641057275069E-42</v>
       </c>
       <c r="E12">
         <v>1</v>

--- a/Sensitivity analysis/Sensitivity analysis.xlsx
+++ b/Sensitivity analysis/Sensitivity analysis.xlsx
@@ -385,16 +385,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.09279336734693877</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="B2">
-        <v>7.74111461817066E-95</v>
+        <v>1.466164569681461E-125</v>
       </c>
       <c r="C2">
-        <v>0.3006306689342403</v>
+        <v>0.2730178202479339</v>
       </c>
       <c r="D2">
-        <v>1.757118450130801E-09</v>
+        <v>3.996458043291421E-13</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -402,16 +402,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.09279336734693877</v>
+        <v>0.07638171487603305</v>
       </c>
       <c r="B3">
-        <v>3.15287278228097E-95</v>
+        <v>1.274550412585945E-125</v>
       </c>
       <c r="C3">
-        <v>0.3013038548752834</v>
+        <v>0.2738571797520661</v>
       </c>
       <c r="D3">
-        <v>2.038928083225326E-09</v>
+        <v>5.109033651971967E-13</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -419,16 +419,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.09325396825396826</v>
+        <v>0.07512267561983471</v>
       </c>
       <c r="B4">
-        <v>7.832201068330619E-95</v>
+        <v>4.959748072234204E-129</v>
       </c>
       <c r="C4">
-        <v>0.3022250566893424</v>
+        <v>0.2748902376033058</v>
       </c>
       <c r="D4">
-        <v>2.465836399110761E-09</v>
+        <v>6.83054889226622E-13</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -436,16 +436,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.09350198412698413</v>
+        <v>0.07366993801652892</v>
       </c>
       <c r="B5">
-        <v>2.165494710383675E-95</v>
+        <v>1.464755745394287E-134</v>
       </c>
       <c r="C5">
-        <v>0.3035359977324263</v>
+        <v>0.275987861570248</v>
       </c>
       <c r="D5">
-        <v>3.266548264181864E-09</v>
+        <v>9.399002162056276E-13</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -453,16 +453,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.09204931972789115</v>
+        <v>0.07231404958677685</v>
       </c>
       <c r="B6">
-        <v>2.522895536326446E-98</v>
+        <v>2.117994792428785E-139</v>
       </c>
       <c r="C6">
-        <v>0.3050240929705215</v>
+        <v>0.2771823347107438</v>
       </c>
       <c r="D6">
-        <v>4.405425148587582E-09</v>
+        <v>1.306802375582837E-12</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -470,16 +470,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.09346655328798185</v>
+        <v>0.07040934917355372</v>
       </c>
       <c r="B7">
-        <v>2.574136387959558E-96</v>
+        <v>1.116261490619566E-145</v>
       </c>
       <c r="C7">
-        <v>0.3062996031746032</v>
+        <v>0.2788610537190083</v>
       </c>
       <c r="D7">
-        <v>5.757819387396599E-09</v>
+        <v>2.107046162779358E-12</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -487,16 +487,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.0939625850340136</v>
+        <v>0.07115185950413223</v>
       </c>
       <c r="B8">
-        <v>8.58899743995105E-96</v>
+        <v>7.359885755436667E-144</v>
       </c>
       <c r="C8">
-        <v>0.3072562358276644</v>
+        <v>0.2801523760330579</v>
       </c>
       <c r="D8">
-        <v>6.961836340262211E-09</v>
+        <v>3.016966664248748E-12</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -504,16 +504,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.09481292517006802</v>
+        <v>0.0699896694214876</v>
       </c>
       <c r="B9">
-        <v>2.001113363283056E-95</v>
+        <v>4.095622318847451E-150</v>
       </c>
       <c r="C9">
-        <v>0.308531746031746</v>
+        <v>0.2814114152892562</v>
       </c>
       <c r="D9">
-        <v>9.021805036605629E-09</v>
+        <v>4.23878594043925E-12</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -521,16 +521,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.09328939909297052</v>
+        <v>0.06895661157024793</v>
       </c>
       <c r="B10">
-        <v>1.303362424043252E-98</v>
+        <v>8.573662691620251E-155</v>
       </c>
       <c r="C10">
-        <v>0.3104804421768708</v>
+        <v>0.2832192665289256</v>
       </c>
       <c r="D10">
-        <v>1.358496678438934E-08</v>
+        <v>7.030981480251125E-12</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -538,16 +538,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.0586734693877551</v>
+        <v>0.049974173553719</v>
       </c>
       <c r="B11">
-        <v>1.526515827962213E-171</v>
+        <v>2.980535662073767E-217</v>
       </c>
       <c r="C11">
-        <v>0.3138463718820862</v>
+        <v>0.2863184400826446</v>
       </c>
       <c r="D11">
-        <v>2.687549391793392E-08</v>
+        <v>1.661893610261474E-11</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -555,16 +555,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.0954861111111111</v>
+        <v>0.07086131198347108</v>
       </c>
       <c r="B12">
-        <v>1.299360424744752E-94</v>
+        <v>3.011010613428227E-147</v>
       </c>
       <c r="C12">
-        <v>0.3160076530612245</v>
+        <v>0.2884491219008264</v>
       </c>
       <c r="D12">
-        <v>4.162341216434452E-08</v>
+        <v>2.950350325541677E-11</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -609,16 +609,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.09279336734693877</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="B2">
-        <v>7.74111461817066E-95</v>
+        <v>1.466164569681461E-125</v>
       </c>
       <c r="C2">
-        <v>0.3006306689342403</v>
+        <v>0.2730178202479339</v>
       </c>
       <c r="D2">
-        <v>1.757118450130801E-09</v>
+        <v>3.996458043291421E-13</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -626,16 +626,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.09275793650793651</v>
+        <v>0.0764139979338843</v>
       </c>
       <c r="B3">
-        <v>5.920034566558455E-95</v>
+        <v>1.175158201549018E-125</v>
       </c>
       <c r="C3">
-        <v>0.2952097505668934</v>
+        <v>0.2686596074380165</v>
       </c>
       <c r="D3">
-        <v>5.054592269885792E-10</v>
+        <v>9.680447067441443E-14</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -643,16 +643,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.09250992063492064</v>
+        <v>0.07634943181818182</v>
       </c>
       <c r="B4">
-        <v>2.861327928869572E-95</v>
+        <v>1.025267381181481E-125</v>
       </c>
       <c r="C4">
-        <v>0.2848639455782313</v>
+        <v>0.2574573863636364</v>
       </c>
       <c r="D4">
-        <v>3.477068775149689E-11</v>
+        <v>1.89126763516196E-15</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -660,16 +660,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.09222647392290249</v>
+        <v>0.0762525826446281</v>
       </c>
       <c r="B5">
-        <v>1.176640673931353E-95</v>
+        <v>7.28716978527044E-126</v>
       </c>
       <c r="C5">
-        <v>0.2689200680272109</v>
+        <v>0.2437370867768595</v>
       </c>
       <c r="D5">
-        <v>3.791320989619202E-13</v>
+        <v>9.311438524626785E-18</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -677,16 +677,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.09268707482993198</v>
+        <v>0.07628486570247933</v>
       </c>
       <c r="B6">
-        <v>5.628995478153802E-95</v>
+        <v>9.080172561633152E-126</v>
       </c>
       <c r="C6">
-        <v>0.2523030045351474</v>
+        <v>0.2239798553719008</v>
       </c>
       <c r="D6">
-        <v>1.490723211478517E-15</v>
+        <v>1.122876180562738E-21</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -694,16 +694,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.09311224489795919</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="B7">
-        <v>2.303549519246324E-94</v>
+        <v>2.793142810612091E-125</v>
       </c>
       <c r="C7">
-        <v>0.2329577664399093</v>
+        <v>0.2051911157024793</v>
       </c>
       <c r="D7">
-        <v>4.916943731261179E-19</v>
+        <v>2.30370260691591E-26</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -711,16 +711,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.09367913832199547</v>
+        <v>0.07654313016528926</v>
       </c>
       <c r="B8">
-        <v>1.341582019926507E-93</v>
+        <v>3.993341805359632E-125</v>
       </c>
       <c r="C8">
-        <v>0.2120535714285714</v>
+        <v>0.1870157541322314</v>
       </c>
       <c r="D8">
-        <v>1.212179892521932E-23</v>
+        <v>4.202235147555409E-32</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -728,16 +728,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.09392715419501134</v>
+        <v>0.07696280991735537</v>
       </c>
       <c r="B9">
-        <v>3.035038437020045E-93</v>
+        <v>4.071238609743224E-124</v>
       </c>
       <c r="C9">
-        <v>0.1915745464852608</v>
+        <v>0.1673876549586777</v>
       </c>
       <c r="D9">
-        <v>3.120680659305024E-29</v>
+        <v>7.970909516588457E-40</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -745,16 +745,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.0946357709750567</v>
+        <v>0.07741477272727272</v>
       </c>
       <c r="B10">
-        <v>4.244920502548199E-92</v>
+        <v>3.817942223198505E-123</v>
       </c>
       <c r="C10">
-        <v>0.1725481859410431</v>
+        <v>0.1500839359504132</v>
       </c>
       <c r="D10">
-        <v>7.356423622756562E-36</v>
+        <v>1.793868007344699E-48</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -762,16 +762,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.0954861111111111</v>
+        <v>0.07789901859504132</v>
       </c>
       <c r="B11">
-        <v>9.120503902334824E-91</v>
+        <v>3.745866828239676E-122</v>
       </c>
       <c r="C11">
-        <v>0.1564271541950113</v>
+        <v>0.1358793904958678</v>
       </c>
       <c r="D11">
-        <v>7.868811920211289E-43</v>
+        <v>3.531214805149533E-57</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -779,16 +779,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.09654903628117914</v>
+        <v>0.0786092458677686</v>
       </c>
       <c r="B12">
-        <v>2.880581339521268E-89</v>
+        <v>1.545231849521979E-120</v>
       </c>
       <c r="C12">
-        <v>0.1437074829931973</v>
+        <v>0.1228693181818182</v>
       </c>
       <c r="D12">
-        <v>1.544113455304959E-49</v>
+        <v>3.440014101266769E-67</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.09279336734693877</v>
+        <v>0.07644628099173553</v>
       </c>
       <c r="B2">
-        <v>7.74111461817066E-95</v>
+        <v>1.466164569681461E-125</v>
       </c>
       <c r="C2">
-        <v>0.3006306689342403</v>
+        <v>0.2730178202479339</v>
       </c>
       <c r="D2">
-        <v>1.757118450130801E-09</v>
+        <v>3.996458043291421E-13</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -850,16 +850,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.09282879818594104</v>
+        <v>0.07634943181818182</v>
       </c>
       <c r="B3">
-        <v>2.859679080330145E-95</v>
+        <v>7.745730903709999E-126</v>
       </c>
       <c r="C3">
-        <v>0.2963081065759637</v>
+        <v>0.2699509297520661</v>
       </c>
       <c r="D3">
-        <v>6.403915084277785E-10</v>
+        <v>1.423598116438747E-13</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.09346655328798185</v>
+        <v>0.07515495867768596</v>
       </c>
       <c r="B4">
-        <v>1.307610453736503E-94</v>
+        <v>5.56394829549598E-129</v>
       </c>
       <c r="C4">
-        <v>0.2868835034013605</v>
+        <v>0.2596526342975207</v>
       </c>
       <c r="D4">
-        <v>5.806612113161748E-11</v>
+        <v>3.995466883016028E-15</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -884,16 +884,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.09431689342403628</v>
+        <v>0.07425103305785125</v>
       </c>
       <c r="B5">
-        <v>3.042995298143445E-94</v>
+        <v>2.860399098219217E-133</v>
       </c>
       <c r="C5">
-        <v>0.2726757369614513</v>
+        <v>0.2476756198347107</v>
       </c>
       <c r="D5">
-        <v>1.116797240163642E-12</v>
+        <v>4.417607425222585E-17</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -901,16 +901,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.09406887755102041</v>
+        <v>0.07337939049586777</v>
       </c>
       <c r="B6">
-        <v>3.444926960185981E-95</v>
+        <v>9.133062212565929E-137</v>
       </c>
       <c r="C6">
-        <v>0.2577593537414966</v>
+        <v>0.2291451446280992</v>
       </c>
       <c r="D6">
-        <v>8.696107123019547E-15</v>
+        <v>1.318888020899135E-20</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.09686791383219955</v>
+        <v>0.07263688016528926</v>
       </c>
       <c r="B7">
-        <v>1.614805408803615E-91</v>
+        <v>9.477737551800367E-140</v>
       </c>
       <c r="C7">
-        <v>0.2394770408163265</v>
+        <v>0.2111957644628099</v>
       </c>
       <c r="D7">
-        <v>6.818541172887411E-18</v>
+        <v>7.37612304235503E-25</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -935,16 +935,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.0988874716553288</v>
+        <v>0.0740573347107438</v>
       </c>
       <c r="B8">
-        <v>9.000903954369589E-89</v>
+        <v>6.373471729976198E-136</v>
       </c>
       <c r="C8">
-        <v>0.2197066326530612</v>
+        <v>0.1947959710743802</v>
       </c>
       <c r="D8">
-        <v>5.834222691731474E-22</v>
+        <v>1.143309695903993E-29</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -952,16 +952,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.101296768707483</v>
+        <v>0.07444473140495868</v>
       </c>
       <c r="B9">
-        <v>3.204234580977685E-86</v>
+        <v>9.080306701740896E-137</v>
       </c>
       <c r="C9">
-        <v>0.1997945011337869</v>
+        <v>0.1757489669421488</v>
       </c>
       <c r="D9">
-        <v>6.905586549531416E-27</v>
+        <v>2.286322698058033E-36</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.1014384920634921</v>
+        <v>0.07428331611570248</v>
       </c>
       <c r="B10">
-        <v>1.770363872676962E-86</v>
+        <v>6.195626809888281E-138</v>
       </c>
       <c r="C10">
-        <v>0.1820082199546485</v>
+        <v>0.1594460227272727</v>
       </c>
       <c r="D10">
-        <v>2.0753453151163E-32</v>
+        <v>1.705603722987035E-43</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -986,16 +986,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.06242913832199547</v>
+        <v>0.05291193181818182</v>
       </c>
       <c r="B11">
-        <v>2.890593069086034E-157</v>
+        <v>7.866884296482967E-201</v>
       </c>
       <c r="C11">
-        <v>0.1674815759637188</v>
+        <v>0.1461776859504132</v>
       </c>
       <c r="D11">
-        <v>8.637967337059903E-38</v>
+        <v>2.130073733334175E-50</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1047689909297052</v>
+        <v>0.07651084710743801</v>
       </c>
       <c r="B12">
-        <v>4.629385688184152E-82</v>
+        <v>8.550486639328399E-132</v>
       </c>
       <c r="C12">
-        <v>0.1569940476190476</v>
+        <v>0.1349108987603306</v>
       </c>
       <c r="D12">
-        <v>2.045641057275069E-42</v>
+        <v>1.656501149504453E-57</v>
       </c>
       <c r="E12">
         <v>1</v>
